--- a/public/downloads/TangActive2025.xlsx
+++ b/public/downloads/TangActive2025.xlsx
@@ -1578,16 +1578,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2472272670808463</v>
+        <v>-0.1785482128339027</v>
       </c>
       <c r="O3" s="5">
         <v>10</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1536179762671256</v>
+        <v>0.1433201682426784</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1536179762671256</v>
+        <v>0.1433201682426784</v>
       </c>
       <c r="R3" s="5">
         <v>10</v>
@@ -1637,16 +1637,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1109370445002553</v>
+        <v>-0.1337253795313131</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3251398681791537</v>
+        <v>0.3241350899578149</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3251398681791537</v>
+        <v>0.3241350899578149</v>
       </c>
       <c r="R4" s="5">
         <v>10</v>
@@ -1696,16 +1696,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.3516437467266112</v>
+        <v>-0.3622497160773435</v>
       </c>
       <c r="O5" s="5">
         <v>10</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2523891213267815</v>
+        <v>0.2509330637740863</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2523891213267815</v>
+        <v>0.2509330637740863</v>
       </c>
       <c r="R5" s="5">
         <v>10</v>
@@ -1755,22 +1755,22 @@
         <v>2</v>
       </c>
       <c r="N6" s="4">
-        <v>0.9309267427486313</v>
+        <v>0.4215237354986758</v>
       </c>
       <c r="O6" s="5">
         <v>7</v>
       </c>
       <c r="P6" s="4">
-        <v>0.9125803591364671</v>
+        <v>0.9396658259181503</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.9772785418714042</v>
+        <v>0.2288629056233937</v>
       </c>
       <c r="R6" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S6" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="25" customHeight="1">
@@ -1814,16 +1814,16 @@
         <v>1</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.4000909600644086</v>
+        <v>0.1537644285578674</v>
       </c>
       <c r="O7" s="5">
         <v>6</v>
       </c>
       <c r="P7" s="4">
-        <v>1.716972961149847</v>
+        <v>1.765651401593643</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.5637022764457505</v>
+        <v>0.107203768711066</v>
       </c>
       <c r="R7" s="5">
         <v>5</v>
@@ -1873,16 +1873,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.4041830929846775</v>
+        <v>-0.3717048400386034</v>
       </c>
       <c r="O8" s="5">
         <v>7</v>
       </c>
       <c r="P8" s="4">
-        <v>0.149510504976428</v>
+        <v>0.1493414987139925</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1343773421788944</v>
+        <v>0.1297375917580266</v>
       </c>
       <c r="R8" s="5">
         <v>7</v>
@@ -1932,16 +1932,16 @@
         <v>1</v>
       </c>
       <c r="N9" s="4">
-        <v>0.5085888202660256</v>
+        <v>-0.04673004169973183</v>
       </c>
       <c r="O9" s="5">
         <v>5</v>
       </c>
       <c r="P9" s="4">
-        <v>1.050445410204213</v>
+        <v>1.084388299194935</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.5597732062812217</v>
+        <v>0.07234012229690867</v>
       </c>
       <c r="R9" s="5">
         <v>4</v>
@@ -1991,13 +1991,13 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>0.8197914509359698</v>
+        <v>0.8236130358260685</v>
       </c>
       <c r="O10" s="5">
         <v>6</v>
       </c>
       <c r="P10" s="4">
-        <v>0.9163772627278297</v>
+        <v>0.915421866505305</v>
       </c>
       <c r="Q10" s="4">
         <v>0.8476758051937727</v>
@@ -2287,16 +2287,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.7540356808620143</v>
+        <v>-0.8946208612323971</v>
       </c>
       <c r="O3" s="5">
         <v>9</v>
       </c>
       <c r="P3" s="4">
-        <v>0.357531103334299</v>
+        <v>0.3294140672602225</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3506250088230669</v>
+        <v>0.3350044332263578</v>
       </c>
       <c r="R3" s="5">
         <v>9</v>
@@ -2346,13 +2346,13 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.8345046217309573</v>
+        <v>-0.9190532655593415</v>
       </c>
       <c r="O4" s="5">
         <v>8</v>
       </c>
       <c r="P4" s="4">
-        <v>0.6666120434918412</v>
+        <v>0.6497023147261644</v>
       </c>
       <c r="Q4" s="4">
         <v>0.3518390568806353</v>
@@ -2405,16 +2405,16 @@
         <v>2</v>
       </c>
       <c r="N5" s="4">
-        <v>-1.734240386940655</v>
+        <v>-1.652073927849415</v>
       </c>
       <c r="O5" s="5">
         <v>9</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4281383484471007</v>
+        <v>0.4136311993934214</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4062898117812842</v>
+        <v>0.3810411507115027</v>
       </c>
       <c r="R5" s="5">
         <v>9</v>
@@ -2464,7 +2464,7 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.22605992515455</v>
+        <v>-0.6737288887379691</v>
       </c>
       <c r="O6" s="5">
         <v>5</v>
@@ -2473,7 +2473,7 @@
         <v>1.482143954314961</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.6699905593571021</v>
+        <v>0.5804567666404182</v>
       </c>
       <c r="R6" s="5">
         <v>5</v>
@@ -2523,16 +2523,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>1.162912623862212</v>
+        <v>1.143978944965056</v>
       </c>
       <c r="O7" s="5">
         <v>5</v>
       </c>
       <c r="P7" s="4">
-        <v>1.668981968938169</v>
+        <v>1.657621761599876</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.4385204811580479</v>
+        <v>0.4347337453786168</v>
       </c>
       <c r="R7" s="5">
         <v>5</v>
@@ -2982,16 +2982,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1612109204509183</v>
+        <v>-0.1549327482100225</v>
       </c>
       <c r="O3" s="5">
         <v>8</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3620547644952569</v>
+        <v>0.3623652986092852</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.08116960122054775</v>
+        <v>0.07998822580285925</v>
       </c>
       <c r="R3" s="5">
         <v>8</v>
@@ -3041,13 +3041,13 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1780436770760831</v>
+        <v>0.1854685538455718</v>
       </c>
       <c r="O4" s="5">
         <v>6</v>
       </c>
       <c r="P4" s="4">
-        <v>0.6011869666626315</v>
+        <v>0.6011869666626314</v>
       </c>
       <c r="Q4" s="4">
         <v>0.2223862327701712</v>
@@ -3100,13 +3100,13 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2330476889255439</v>
+        <v>-0.2226554676571197</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>0.5947060859827732</v>
+        <v>0.5967845302364581</v>
       </c>
       <c r="Q5" s="4">
         <v>0.1204996286590626</v>
@@ -3159,16 +3159,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>0.04925230117506807</v>
+        <v>0.0922961506251827</v>
       </c>
       <c r="O6" s="5">
         <v>5</v>
       </c>
       <c r="P6" s="4">
-        <v>0.7183260603461574</v>
+        <v>0.7097172904561345</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.202431029496411</v>
+        <v>0.193822259606388</v>
       </c>
       <c r="R6" s="5">
         <v>5</v>
@@ -3218,13 +3218,13 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>0.1523738475079497</v>
+        <v>0.1159530542571239</v>
       </c>
       <c r="O7" s="5">
         <v>6</v>
       </c>
       <c r="P7" s="4">
-        <v>0.6578029129244577</v>
+        <v>0.6723712302247881</v>
       </c>
       <c r="Q7" s="4">
         <v>0.1089741102385498</v>
@@ -3277,16 +3277,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.3945203184414993</v>
+        <v>-0.4220873495609681</v>
       </c>
       <c r="O8" s="5">
         <v>5</v>
       </c>
       <c r="P8" s="4">
-        <v>0.467424036169617</v>
+        <v>0.4521090188810233</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.09347596892656143</v>
+        <v>0.08796256270266767</v>
       </c>
       <c r="R8" s="5">
         <v>5</v>
@@ -3687,16 +3687,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2907231616773061</v>
+        <v>-0.2430093953371397</v>
       </c>
       <c r="O3" s="5">
         <v>10</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2020627514051739</v>
+        <v>0.1928065021769726</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2020627514051739</v>
+        <v>0.1928065021769726</v>
       </c>
       <c r="R3" s="5">
         <v>10</v>
@@ -3746,7 +3746,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.5162187725320109</v>
+        <v>-0.5183315358117397</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
@@ -3805,16 +3805,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.7360326039575739</v>
+        <v>-0.6865428282544599</v>
       </c>
       <c r="O5" s="5">
         <v>10</v>
       </c>
       <c r="P5" s="4">
-        <v>0.292415500965144</v>
+        <v>0.290478060427995</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.292415500965144</v>
+        <v>0.290478060427995</v>
       </c>
       <c r="R5" s="5">
         <v>10</v>
@@ -3864,16 +3864,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>0.1671250611820142</v>
+        <v>0.1714030823422945</v>
       </c>
       <c r="O6" s="5">
         <v>5</v>
       </c>
       <c r="P6" s="4">
-        <v>1.995096234398225</v>
+        <v>1.992529421702056</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.2392446570319589</v>
+        <v>0.2383890527999029</v>
       </c>
       <c r="R6" s="5">
         <v>5</v>
@@ -3923,16 +3923,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>0.09536563632864273</v>
+        <v>0.1509099012619117</v>
       </c>
       <c r="O7" s="5">
         <v>5</v>
       </c>
       <c r="P7" s="4">
-        <v>3.687559336458653</v>
+        <v>3.70977704243196</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.09132463026151527</v>
+        <v>0.08021577727486147</v>
       </c>
       <c r="R7" s="5">
         <v>5</v>
@@ -3982,16 +3982,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.4602829483888594</v>
+        <v>-0.5184095378936036</v>
       </c>
       <c r="O8" s="5">
         <v>7</v>
       </c>
       <c r="P8" s="4">
-        <v>0.1469425333250131</v>
+        <v>0.1404840233800415</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1417868220819308</v>
+        <v>0.133483023581253</v>
       </c>
       <c r="R8" s="5">
         <v>7</v>
@@ -4392,7 +4392,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3430432128705433</v>
+        <v>-0.3171343989524757</v>
       </c>
       <c r="O3" s="5">
         <v>10</v>
@@ -4451,16 +4451,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1232268482461222</v>
+        <v>-0.2178092079666385</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3249665656060097</v>
+        <v>0.3108048513953691</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3249665656060097</v>
+        <v>0.3108048513953691</v>
       </c>
       <c r="R4" s="5">
         <v>10</v>
@@ -4510,16 +4510,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.338771985747735</v>
+        <v>-0.3998488605393504</v>
       </c>
       <c r="O5" s="5">
         <v>10</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2355192282196367</v>
+        <v>0.2242052076180698</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2355192282196367</v>
+        <v>0.2242052076180698</v>
       </c>
       <c r="R5" s="5">
         <v>10</v>
@@ -4569,22 +4569,22 @@
         <v>1</v>
       </c>
       <c r="N6" s="4">
-        <v>0.8086265029903318</v>
+        <v>0.4574366157175973</v>
       </c>
       <c r="O6" s="5">
         <v>7</v>
       </c>
       <c r="P6" s="4">
-        <v>1.343174101194745</v>
+        <v>1.379807118485769</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.8607308739874683</v>
+        <v>0.5064908922807566</v>
       </c>
       <c r="R6" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="25" customHeight="1">
@@ -4628,22 +4628,22 @@
         <v>3</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.8199588028628568</v>
+        <v>0.1007711513921095</v>
       </c>
       <c r="O7" s="5">
         <v>8</v>
       </c>
       <c r="P7" s="4">
-        <v>1.38221074203102</v>
+        <v>1.384122257199488</v>
       </c>
       <c r="Q7" s="4">
-        <v>1.192016187277659</v>
+        <v>0.125436682219879</v>
       </c>
       <c r="R7" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S7" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="25" customHeight="1">
@@ -4687,16 +4687,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.04217094052624556</v>
+        <v>-0.07686466389714042</v>
       </c>
       <c r="O8" s="5">
         <v>7</v>
       </c>
       <c r="P8" s="4">
-        <v>0.1709415231175843</v>
+        <v>0.1534118800134618</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1799391562728525</v>
+        <v>0.1673135361020936</v>
       </c>
       <c r="R8" s="5">
         <v>7</v>
@@ -4746,22 +4746,22 @@
         <v>2</v>
       </c>
       <c r="N9" s="4">
-        <v>0.9751416962305181</v>
+        <v>0.476318394728878</v>
       </c>
       <c r="O9" s="5">
         <v>6</v>
       </c>
       <c r="P9" s="4">
-        <v>1.064217539647871</v>
+        <v>1.084475421477691</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.8707372462530557</v>
+        <v>0.4662355275562732</v>
       </c>
       <c r="R9" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S9" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="25" customHeight="1">
@@ -5099,7 +5099,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4378493118085316</v>
+        <v>-0.4141650864839903</v>
       </c>
       <c r="O3" s="5">
         <v>10</v>
@@ -5158,16 +5158,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.6492203861489543</v>
+        <v>-0.7437749209202593</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2504219723123242</v>
+        <v>0.2287976252206136</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2504219723123242</v>
+        <v>0.2287976252206136</v>
       </c>
       <c r="R4" s="5">
         <v>10</v>
@@ -5217,16 +5217,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-1.095139859893243</v>
+        <v>-1.187961846637336</v>
       </c>
       <c r="O5" s="5">
         <v>10</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1466132609080523</v>
+        <v>0.1318412558917771</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1466132609080523</v>
+        <v>0.1318412558917771</v>
       </c>
       <c r="R5" s="5">
         <v>10</v>
@@ -5333,16 +5333,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>0.5370940851964405</v>
+        <v>0.4896803431402077</v>
       </c>
       <c r="O7" s="5">
         <v>5</v>
       </c>
       <c r="P7" s="4">
-        <v>5.003453616183397</v>
+        <v>4.975005370949657</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1448966369766276</v>
+        <v>0.1354138885653811</v>
       </c>
       <c r="R7" s="5">
         <v>5</v>
@@ -5392,16 +5392,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.8068428284732363</v>
+        <v>-0.7259636471608246</v>
       </c>
       <c r="O8" s="5">
         <v>8</v>
       </c>
       <c r="P8" s="4">
-        <v>0.2115081293043962</v>
+        <v>0.2039341327209614</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1581516263627236</v>
+        <v>0.139520982542308</v>
       </c>
       <c r="R8" s="5">
         <v>8</v>
@@ -5802,16 +5802,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1069012450970776</v>
+        <v>-0.07111954614447313</v>
       </c>
       <c r="O3" s="5">
         <v>10</v>
       </c>
       <c r="P3" s="4">
-        <v>0.08456141794738994</v>
+        <v>0.07937553244264564</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.08456141794738994</v>
+        <v>0.07937553244264564</v>
       </c>
       <c r="R3" s="5">
         <v>10</v>
@@ -5861,16 +5861,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.04313992411047609</v>
+        <v>0.03011949136629255</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2344486896687848</v>
+        <v>0.2164923966352846</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2344486896687848</v>
+        <v>0.2164923966352846</v>
       </c>
       <c r="R4" s="5">
         <v>10</v>
@@ -5920,16 +5920,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.03092647334501998</v>
+        <v>0.01835434821259696</v>
       </c>
       <c r="O5" s="5">
         <v>9</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2167678829793404</v>
+        <v>0.2142534579528558</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.07353567027659529</v>
+        <v>0.07213876748410383</v>
       </c>
       <c r="R5" s="5">
         <v>9</v>
@@ -5979,16 +5979,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>0.1174042882695383</v>
+        <v>0.1516784055856419</v>
       </c>
       <c r="O6" s="5">
         <v>9</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1517750102846268</v>
+        <v>0.1492045756116511</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.153312383369427</v>
+        <v>0.1466481095865536</v>
       </c>
       <c r="R6" s="5">
         <v>9</v>
@@ -6038,16 +6038,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.223488627190087</v>
+        <v>-0.2140675898117685</v>
       </c>
       <c r="O7" s="5">
         <v>10</v>
       </c>
       <c r="P7" s="4">
-        <v>0.05657204060610893</v>
+        <v>0.05622704652998305</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.05657204060610893</v>
+        <v>0.05622704652998305</v>
       </c>
       <c r="R7" s="5">
         <v>10</v>
@@ -6097,16 +6097,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>0.05694291660259765</v>
+        <v>0.05044272751908263</v>
       </c>
       <c r="O8" s="5">
         <v>8</v>
       </c>
       <c r="P8" s="4">
-        <v>0.05566760144700428</v>
+        <v>0.05373676480224226</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.05040329685384615</v>
+        <v>0.04904362926392825</v>
       </c>
       <c r="R8" s="5">
         <v>8</v>
@@ -6156,7 +6156,7 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>0.2062294766874929</v>
+        <v>0.2195473684696789</v>
       </c>
       <c r="O9" s="5">
         <v>8</v>
@@ -6215,7 +6215,7 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>0.147125274157088</v>
+        <v>0.1568181991897997</v>
       </c>
       <c r="O10" s="5">
         <v>7</v>
@@ -6224,7 +6224,7 @@
         <v>0.2477711551110051</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.08076772179485488</v>
+        <v>0.07938301821875322</v>
       </c>
       <c r="R10" s="5">
         <v>7</v>
@@ -6511,16 +6511,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4073673534192409</v>
+        <v>-0.3606648117856643</v>
       </c>
       <c r="O3" s="5">
         <v>10</v>
       </c>
       <c r="P3" s="4">
-        <v>0.09731818353408414</v>
+        <v>0.08915888865158764</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.09731818353408414</v>
+        <v>0.08915888865158764</v>
       </c>
       <c r="R3" s="5">
         <v>10</v>
@@ -6570,7 +6570,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3794379852737815</v>
+        <v>-0.2996402915523557</v>
       </c>
       <c r="O4" s="5">
         <v>9</v>
@@ -6579,7 +6579,7 @@
         <v>0.2307776764457461</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1847128678180895</v>
+        <v>0.1758464574045977</v>
       </c>
       <c r="R4" s="5">
         <v>9</v>
@@ -6629,16 +6629,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.6215665805124381</v>
+        <v>-0.5505206704511485</v>
       </c>
       <c r="O5" s="5">
         <v>10</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1561157939195632</v>
+        <v>0.1478560783303408</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1561157939195632</v>
+        <v>0.1478560783303408</v>
       </c>
       <c r="R5" s="5">
         <v>10</v>
@@ -6688,7 +6688,7 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.6982140926346925</v>
+        <v>-0.6413445288998663</v>
       </c>
       <c r="O6" s="5">
         <v>9</v>
@@ -6697,7 +6697,7 @@
         <v>0.1555528005912038</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1301134727473672</v>
+        <v>0.1237946323323865</v>
       </c>
       <c r="R6" s="5">
         <v>9</v>
@@ -6747,16 +6747,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>0.4738856913499599</v>
+        <v>0.4367260380240356</v>
       </c>
       <c r="O7" s="5">
         <v>10</v>
       </c>
       <c r="P7" s="4">
-        <v>0.1134014674170918</v>
+        <v>0.108694290814277</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1134014674170918</v>
+        <v>0.108694290814277</v>
       </c>
       <c r="R7" s="5">
         <v>10</v>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.6057550880360139</v>
+        <v>-0.5910290151842776</v>
       </c>
       <c r="O8" s="5">
         <v>8</v>
       </c>
       <c r="P8" s="4">
-        <v>0.07454887528081405</v>
+        <v>0.07618510559767364</v>
       </c>
       <c r="Q8" s="4">
         <v>0.06520246693433451</v>
@@ -6865,16 +6865,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.8225910510299932</v>
+        <v>-0.8088606084602183</v>
       </c>
       <c r="O9" s="5">
         <v>8</v>
       </c>
       <c r="P9" s="4">
-        <v>0.06931132624411862</v>
+        <v>0.06926956275490648</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.06931132624411862</v>
+        <v>0.06926956275490648</v>
       </c>
       <c r="R9" s="5">
         <v>8</v>
@@ -6924,16 +6924,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.9624354432627815</v>
+        <v>-0.9437523139858399</v>
       </c>
       <c r="O10" s="5">
         <v>5</v>
       </c>
       <c r="P10" s="4">
-        <v>0.1572607031004176</v>
+        <v>0.161931485419653</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.07457401980983236</v>
+        <v>0.07083739395444404</v>
       </c>
       <c r="R10" s="5">
         <v>5</v>
@@ -7220,16 +7220,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1297310191192141</v>
+        <v>-0.0817120965475624</v>
       </c>
       <c r="O3" s="5">
         <v>10</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1182523945815183</v>
+        <v>0.1052093761885885</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1182523945815183</v>
+        <v>0.1052093761885885</v>
       </c>
       <c r="R3" s="5">
         <v>10</v>
@@ -7279,16 +7279,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.0471057206406944</v>
+        <v>0.05334501690596438</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2969138665450771</v>
+        <v>0.2781347826545201</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2969138665450771</v>
+        <v>0.2781347826545201</v>
       </c>
       <c r="R4" s="5">
         <v>10</v>
@@ -7338,16 +7338,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.07296222028961452</v>
+        <v>0.04172534488317847</v>
       </c>
       <c r="O5" s="5">
         <v>10</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2660995115523097</v>
+        <v>0.2300399092753832</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2660995115523097</v>
+        <v>0.2300399092753832</v>
       </c>
       <c r="R5" s="5">
         <v>10</v>
@@ -7397,16 +7397,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>0.1085849598110175</v>
+        <v>0.1472026928095715</v>
       </c>
       <c r="O6" s="5">
         <v>9</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1797632180315206</v>
+        <v>0.1724560844093503</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1944837626141623</v>
+        <v>0.1820738660341337</v>
       </c>
       <c r="R6" s="5">
         <v>9</v>
@@ -7456,16 +7456,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.2399277118987947</v>
+        <v>-0.2324449275110896</v>
       </c>
       <c r="O7" s="5">
         <v>10</v>
       </c>
       <c r="P7" s="4">
-        <v>0.07488194017468712</v>
+        <v>0.07383765579653234</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.07488194017468712</v>
+        <v>0.07383765579653234</v>
       </c>
       <c r="R7" s="5">
         <v>10</v>
@@ -7515,16 +7515,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>0.08879145531475759</v>
+        <v>0.09601540603034664</v>
       </c>
       <c r="O8" s="5">
         <v>7</v>
       </c>
       <c r="P8" s="4">
-        <v>0.1038257073423973</v>
+        <v>0.1046283685330184</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.0612274635768729</v>
+        <v>0.06019547061750303</v>
       </c>
       <c r="R8" s="5">
         <v>7</v>
@@ -7574,7 +7574,7 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>0.262768274946458</v>
+        <v>0.2702407632168664</v>
       </c>
       <c r="O9" s="5">
         <v>7</v>
@@ -7583,7 +7583,7 @@
         <v>0.09857294880385531</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.09039695718064898</v>
+        <v>0.08932945885630492</v>
       </c>
       <c r="R9" s="5">
         <v>7</v>
@@ -7633,7 +7633,7 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>0.1898207389895545</v>
+        <v>0.2002159403418773</v>
       </c>
       <c r="O10" s="5">
         <v>7</v>
@@ -7642,7 +7642,7 @@
         <v>0.3103192487815551</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.1347861723230321</v>
+        <v>0.1333011435584146</v>
       </c>
       <c r="R10" s="5">
         <v>7</v>
@@ -7929,16 +7929,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3382531332768991</v>
+        <v>-0.3254948109460933</v>
       </c>
       <c r="O3" s="5">
         <v>10</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1192488534757371</v>
+        <v>0.1186022209847636</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1192488534757371</v>
+        <v>0.1186022209847636</v>
       </c>
       <c r="R3" s="5">
         <v>10</v>
@@ -7988,7 +7988,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.4030709117665506</v>
+        <v>-0.3897555022667447</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
@@ -8047,16 +8047,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.5054547357344397</v>
+        <v>-0.4633840144052064</v>
       </c>
       <c r="O5" s="5">
         <v>10</v>
       </c>
       <c r="P5" s="4">
-        <v>0.122005486226134</v>
+        <v>0.1154400624669734</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.122005486226134</v>
+        <v>0.1154400624669734</v>
       </c>
       <c r="R5" s="5">
         <v>10</v>
@@ -8106,16 +8106,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.5147124486080404</v>
+        <v>-0.4530900511163622</v>
       </c>
       <c r="O6" s="5">
         <v>10</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1376648674750931</v>
+        <v>0.1288831565973055</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1376648674750931</v>
+        <v>0.1288831565973055</v>
       </c>
       <c r="R6" s="5">
         <v>10</v>
@@ -8165,7 +8165,7 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>0.4458783807211713</v>
+        <v>0.4395527321540857</v>
       </c>
       <c r="O7" s="5">
         <v>10</v>
@@ -8224,16 +8224,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.2165268483804765</v>
+        <v>-0.1785718470819564</v>
       </c>
       <c r="O8" s="5">
         <v>8</v>
       </c>
       <c r="P8" s="4">
-        <v>0.100595701584513</v>
+        <v>0.09358911710823214</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1085506294202884</v>
+        <v>0.1051629164467349</v>
       </c>
       <c r="R8" s="5">
         <v>8</v>
@@ -8283,16 +8283,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.4292578841923578</v>
+        <v>-0.4681422339054437</v>
       </c>
       <c r="O9" s="5">
         <v>8</v>
       </c>
       <c r="P9" s="4">
-        <v>0.0936922650653661</v>
+        <v>0.08488809873777559</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.0936922650653661</v>
+        <v>0.08488809873777559</v>
       </c>
       <c r="R9" s="5">
         <v>8</v>
@@ -8342,16 +8342,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.57706315348455</v>
+        <v>-0.5653806641348638</v>
       </c>
       <c r="O10" s="5">
         <v>6</v>
       </c>
       <c r="P10" s="4">
-        <v>0.192179838217247</v>
+        <v>0.1922441707683662</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.07381383580564833</v>
+        <v>0.07000544942391181</v>
       </c>
       <c r="R10" s="5">
         <v>6</v>
@@ -8602,13 +8602,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>0.8088980526884336</v>
+        <v>0.8000602229208367</v>
       </c>
       <c r="I3" s="4">
-        <v>0.2208484740757161</v>
+        <v>0.2158559051998468</v>
       </c>
       <c r="J3" s="4">
-        <v>2.906474882168235</v>
+        <v>2.89910464041123</v>
       </c>
       <c r="K3" s="4">
         <v>85.17132779037554</v>
@@ -8652,13 +8652,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <v>0.4225035853319302</v>
+        <v>0.4122041622959157</v>
       </c>
       <c r="I4" s="4">
-        <v>0.2884448097020475</v>
+        <v>0.2708241932899701</v>
       </c>
       <c r="J4" s="4">
-        <v>0.3196012104707965</v>
+        <v>0.3367881261144282</v>
       </c>
       <c r="K4" s="4">
         <v>83.23843117493897</v>
@@ -8702,13 +8702,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <v>0.3920199757050572</v>
+        <v>0.3761851287825625</v>
       </c>
       <c r="I5" s="4">
-        <v>0.2632940592547137</v>
+        <v>0.2515988531035079</v>
       </c>
       <c r="J5" s="4">
-        <v>0.3646144361194788</v>
+        <v>0.3536673242583394</v>
       </c>
       <c r="K5" s="4">
         <v>82.12018140589535</v>
@@ -8752,13 +8752,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <v>0.4572140086277924</v>
+        <v>0.4502645964749706</v>
       </c>
       <c r="I6" s="4">
-        <v>0.3680574590895655</v>
+        <v>0.3576207755582855</v>
       </c>
       <c r="J6" s="4">
-        <v>0.5972606347908183</v>
+        <v>0.5937945064683452</v>
       </c>
       <c r="K6" s="4">
         <v>82.41286638112035</v>
@@ -8784,13 +8784,13 @@
         <v>21</v>
       </c>
       <c r="B7" s="3">
-        <v>66.66666666666666</v>
+        <v>72.83950617283951</v>
       </c>
       <c r="C7" s="3">
         <v>6.172839506172839</v>
       </c>
       <c r="D7" s="3">
-        <v>27.16049382716049</v>
+        <v>20.98765432098765</v>
       </c>
       <c r="E7" s="3">
         <v>2.469135802469136</v>
@@ -8799,16 +8799,16 @@
         <v>12.34567901234568</v>
       </c>
       <c r="G7" s="3">
-        <v>12.34567901234568</v>
+        <v>6.172839506172839</v>
       </c>
       <c r="H7" s="4">
-        <v>1.077883048269411</v>
+        <v>0.9600017064275798</v>
       </c>
       <c r="I7" s="4">
-        <v>0.2992868359048415</v>
+        <v>0.1962016585612373</v>
       </c>
       <c r="J7" s="4">
-        <v>1.469756484428174</v>
+        <v>1.475809909494139</v>
       </c>
       <c r="K7" s="4">
         <v>92.43260267069796</v>
@@ -8834,13 +8834,13 @@
         <v>22</v>
       </c>
       <c r="B8" s="3">
-        <v>75.30864197530865</v>
+        <v>72.83950617283951</v>
       </c>
       <c r="C8" s="3">
         <v>4.938271604938271</v>
       </c>
       <c r="D8" s="3">
-        <v>19.75308641975309</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="E8" s="3">
         <v>1.234567901234568</v>
@@ -8849,16 +8849,16 @@
         <v>16.04938271604938</v>
       </c>
       <c r="G8" s="3">
-        <v>2.469135802469136</v>
+        <v>4.938271604938271</v>
       </c>
       <c r="H8" s="4">
-        <v>0.70983331376515</v>
+        <v>0.7208509868522319</v>
       </c>
       <c r="I8" s="4">
-        <v>0.4255396828867395</v>
+        <v>0.2689660309418083</v>
       </c>
       <c r="J8" s="4">
-        <v>1.086025129271426</v>
+        <v>1.099364260699071</v>
       </c>
       <c r="K8" s="4">
         <v>87.85252372553964</v>
@@ -8902,13 +8902,13 @@
         <v>2.469135802469136</v>
       </c>
       <c r="H9" s="4">
-        <v>1.388747558677067</v>
+        <v>1.379995198031175</v>
       </c>
       <c r="I9" s="4">
-        <v>0.45336547116153</v>
+        <v>0.4339602206387628</v>
       </c>
       <c r="J9" s="4">
-        <v>1.045592976589278</v>
+        <v>1.057848780623811</v>
       </c>
       <c r="K9" s="4">
         <v>73.96951373141827</v>
@@ -8952,13 +8952,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0.5939977840638939</v>
+        <v>0.5933267976710896</v>
       </c>
       <c r="I10" s="4">
-        <v>0.1694121556451922</v>
+        <v>0.1677441997303778</v>
       </c>
       <c r="J10" s="4">
-        <v>0.2305323892029105</v>
+        <v>0.2281517026195693</v>
       </c>
       <c r="K10" s="4">
         <v>62.71688922482588</v>
@@ -9002,13 +9002,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <v>1.023131364531333</v>
+        <v>1.023457851514212</v>
       </c>
       <c r="I11" s="4">
-        <v>0.2561402137793204</v>
+        <v>0.2519604724474696</v>
       </c>
       <c r="J11" s="4">
-        <v>2.923346787194727</v>
+        <v>2.929454501296636</v>
       </c>
       <c r="K11" s="4">
         <v>85.76299655664715</v>
@@ -9034,13 +9034,13 @@
         <v>26</v>
       </c>
       <c r="B12" s="3">
-        <v>77.77777777777779</v>
+        <v>72.83950617283951</v>
       </c>
       <c r="C12" s="3">
         <v>12.34567901234568</v>
       </c>
       <c r="D12" s="3">
-        <v>9.876543209876543</v>
+        <v>14.81481481481481</v>
       </c>
       <c r="E12" s="3">
         <v>0</v>
@@ -9049,16 +9049,16 @@
         <v>8.641975308641975</v>
       </c>
       <c r="G12" s="3">
-        <v>1.234567901234568</v>
+        <v>6.172839506172839</v>
       </c>
       <c r="H12" s="4">
-        <v>0.790684060234821</v>
+        <v>0.7923505323727753</v>
       </c>
       <c r="I12" s="4">
-        <v>0.5038945333085972</v>
+        <v>0.3017944475477172</v>
       </c>
       <c r="J12" s="4">
-        <v>1.329305242639246</v>
+        <v>1.339964702381195</v>
       </c>
       <c r="K12" s="4">
         <v>92.1084236163599</v>
@@ -9102,13 +9102,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <v>1.546701047861032</v>
+        <v>1.537853986840438</v>
       </c>
       <c r="I13" s="4">
-        <v>0.2508994494173878</v>
+        <v>0.2408919063156126</v>
       </c>
       <c r="J13" s="4">
-        <v>4.186661190885076</v>
+        <v>4.186111589891408</v>
       </c>
       <c r="K13" s="4">
         <v>84.04048038968651</v>
@@ -9152,13 +9152,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <v>0.1390768267496038</v>
+        <v>0.135334877947861</v>
       </c>
       <c r="I14" s="4">
-        <v>0.1058246294022839</v>
+        <v>0.1015089375460465</v>
       </c>
       <c r="J14" s="4">
-        <v>0.1322371364980893</v>
+        <v>0.1283554565187137</v>
       </c>
       <c r="K14" s="4">
         <v>92.8898966994206</v>
@@ -9202,13 +9202,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0.1942826000349858</v>
+        <v>0.1923134192046967</v>
       </c>
       <c r="I15" s="4">
-        <v>0.1686558554963745</v>
+        <v>0.1636971208289119</v>
       </c>
       <c r="J15" s="4">
-        <v>0.1699002690740072</v>
+        <v>0.1658283038505358</v>
       </c>
       <c r="K15" s="4">
         <v>95.00083984210963</v>
@@ -9252,13 +9252,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <v>0.1821414784627025</v>
+        <v>0.1728191664270014</v>
       </c>
       <c r="I16" s="4">
-        <v>0.1658908848481338</v>
+        <v>0.1548770101955437</v>
       </c>
       <c r="J16" s="4">
-        <v>0.1827033427097575</v>
+        <v>0.1707111631452392</v>
       </c>
       <c r="K16" s="4">
         <v>92.23859914336104</v>
@@ -9302,13 +9302,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <v>0.1585148344585564</v>
+        <v>0.1548985924613031</v>
       </c>
       <c r="I17" s="4">
-        <v>0.1490853167853728</v>
+        <v>0.1454447580324015</v>
       </c>
       <c r="J17" s="4">
-        <v>0.145937281137573</v>
+        <v>0.1417217225684423</v>
       </c>
       <c r="K17" s="4">
         <v>91.89678340471987</v>
@@ -10367,13 +10367,13 @@
         <v>21</v>
       </c>
       <c r="B7" s="5">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C7" s="5">
         <v>5</v>
       </c>
       <c r="D7" s="5">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E7" s="5">
         <v>2</v>
@@ -10382,7 +10382,7 @@
         <v>10</v>
       </c>
       <c r="G7" s="5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H7" s="5">
         <v>2</v>
@@ -10411,13 +10411,13 @@
         <v>22</v>
       </c>
       <c r="B8" s="5">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C8" s="5">
         <v>4</v>
       </c>
       <c r="D8" s="5">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E8" s="5">
         <v>1</v>
@@ -10426,7 +10426,7 @@
         <v>13</v>
       </c>
       <c r="G8" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H8" s="5">
         <v>1</v>
@@ -10587,13 +10587,13 @@
         <v>26</v>
       </c>
       <c r="B12" s="5">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C12" s="5">
         <v>10</v>
       </c>
       <c r="D12" s="5">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E12" s="5">
         <v>0</v>
@@ -10602,7 +10602,7 @@
         <v>7</v>
       </c>
       <c r="G12" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H12" s="5">
         <v>0</v>
@@ -11005,7 +11005,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3541537570752553</v>
+        <v>-0.3633521271767677</v>
       </c>
       <c r="O3" s="5">
         <v>10</v>
@@ -11064,16 +11064,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.371366134287382</v>
+        <v>-0.4738858643213462</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3059663644141983</v>
+        <v>0.2872676689163199</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3059663644141983</v>
+        <v>0.2872676689163199</v>
       </c>
       <c r="R4" s="5">
         <v>10</v>
@@ -11123,7 +11123,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.7736565816187067</v>
+        <v>-0.7862456633374677</v>
       </c>
       <c r="O5" s="5">
         <v>10</v>
@@ -11239,16 +11239,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>0.2686785864629201</v>
+        <v>0.1810742532688892</v>
       </c>
       <c r="O7" s="5">
         <v>5</v>
       </c>
       <c r="P7" s="4">
-        <v>1.624405764620896</v>
+        <v>1.571843164704478</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1539151916641276</v>
+        <v>0.1363943250253215</v>
       </c>
       <c r="R7" s="5">
         <v>5</v>
@@ -11298,13 +11298,13 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.7047183337854221</v>
+        <v>-0.7014670767530333</v>
       </c>
       <c r="O8" s="5">
         <v>8</v>
       </c>
       <c r="P8" s="4">
-        <v>0.1363351359209951</v>
+        <v>0.1359738851396186</v>
       </c>
       <c r="Q8" s="4">
         <v>0.1174579317867028</v>
@@ -11708,16 +11708,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.6373539256848744</v>
+        <v>-0.682296581006085</v>
       </c>
       <c r="O3" s="5">
         <v>10</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1173814377997769</v>
+        <v>0.1067763976316201</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1173814377997769</v>
+        <v>0.1067763976316201</v>
       </c>
       <c r="R3" s="5">
         <v>10</v>
@@ -11767,16 +11767,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.249893627815052</v>
+        <v>-0.5066600669015315</v>
       </c>
       <c r="O4" s="5">
         <v>9</v>
       </c>
       <c r="P4" s="4">
-        <v>0.6212407814146396</v>
+        <v>0.5698874935973436</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.5807195967207031</v>
+        <v>0.5521899923777609</v>
       </c>
       <c r="R4" s="5">
         <v>9</v>
@@ -11826,16 +11826,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-1.018430888210787</v>
+        <v>-1.156477832366363</v>
       </c>
       <c r="O5" s="5">
         <v>8</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3109778385023674</v>
+        <v>0.2853690977732185</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3254711625336313</v>
+        <v>0.2934602366221952</v>
       </c>
       <c r="R5" s="5">
         <v>8</v>
@@ -11885,16 +11885,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.2084636254573221</v>
+        <v>-0.3270528966459096</v>
       </c>
       <c r="O6" s="5">
         <v>6</v>
       </c>
       <c r="P6" s="4">
-        <v>0.3373363305603562</v>
+        <v>0.3433906127327646</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.3398971227110855</v>
+        <v>0.3104578359355704</v>
       </c>
       <c r="R6" s="5">
         <v>6</v>
@@ -11944,7 +11944,7 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>0.2415260748271572</v>
+        <v>0.1270181673025945</v>
       </c>
       <c r="O7" s="5">
         <v>9</v>
@@ -11953,7 +11953,7 @@
         <v>0.1883291316400573</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.2069458924754908</v>
+        <v>0.1942227916394283</v>
       </c>
       <c r="R7" s="5">
         <v>9</v>
@@ -12003,16 +12003,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.7011198230480659</v>
+        <v>-0.5976218066134606</v>
       </c>
       <c r="O8" s="5">
         <v>5</v>
       </c>
       <c r="P8" s="4">
-        <v>0.3642004407332731</v>
+        <v>0.3757002203371182</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1361832595069427</v>
+        <v>0.1154836562200217</v>
       </c>
       <c r="R8" s="5">
         <v>5</v>
@@ -12062,16 +12062,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.2780788823001785</v>
+        <v>-0.339390590765106</v>
       </c>
       <c r="O9" s="5">
         <v>5</v>
       </c>
       <c r="P9" s="4">
-        <v>0.2635888353488554</v>
+        <v>0.2482609082326235</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.2145605038356734</v>
+        <v>0.2022981621426879</v>
       </c>
       <c r="R9" s="5">
         <v>5</v>
@@ -12121,7 +12121,7 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.6732823095323207</v>
+        <v>-0.7303505073468841</v>
       </c>
       <c r="O10" s="5">
         <v>6</v>
@@ -12417,16 +12417,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2838231923993185</v>
+        <v>-0.2381579762804904</v>
       </c>
       <c r="O3" s="5">
         <v>9</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1634194325472991</v>
+        <v>0.1599539639297291</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.137420047884074</v>
+        <v>0.128495614295793</v>
       </c>
       <c r="R3" s="5">
         <v>9</v>
@@ -12476,16 +12476,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.2306649400834431</v>
+        <v>-0.01148796073903213</v>
       </c>
       <c r="O4" s="5">
         <v>8</v>
       </c>
       <c r="P4" s="4">
-        <v>0.495450119049201</v>
+        <v>0.4057077335841314</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3741173234643611</v>
+        <v>0.3224775668386428</v>
       </c>
       <c r="R4" s="5">
         <v>8</v>
@@ -12535,13 +12535,13 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.3060154227396197</v>
+        <v>-0.3693607271088695</v>
       </c>
       <c r="O5" s="5">
         <v>8</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3571972833660766</v>
+        <v>0.3445282224922266</v>
       </c>
       <c r="Q5" s="4">
         <v>0.2699693437398309</v>
@@ -12594,16 +12594,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>0.5552225442070267</v>
+        <v>0.437244470231235</v>
       </c>
       <c r="O6" s="5">
         <v>8</v>
       </c>
       <c r="P6" s="4">
-        <v>0.3787474578877664</v>
+        <v>0.3729363150378049</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.3507633223223365</v>
+        <v>0.3434993937598847</v>
       </c>
       <c r="R6" s="5">
         <v>8</v>
@@ -12653,16 +12653,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.01906680792631556</v>
+        <v>0.02449197410896886</v>
       </c>
       <c r="O7" s="5">
         <v>9</v>
       </c>
       <c r="P7" s="4">
-        <v>0.3352380357411878</v>
+        <v>0.3246504322632973</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.272137899871953</v>
+        <v>0.255534031337043</v>
       </c>
       <c r="R7" s="5">
         <v>9</v>
@@ -12712,16 +12712,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.3675297905123444</v>
+        <v>-0.3614141302969074</v>
       </c>
       <c r="O8" s="5">
         <v>5</v>
       </c>
       <c r="P8" s="4">
-        <v>0.3362194891700508</v>
+        <v>0.3355399713683356</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1764849347074051</v>
+        <v>0.1752618026643177</v>
       </c>
       <c r="R8" s="5">
         <v>5</v>
@@ -12771,16 +12771,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.009448487424898693</v>
+        <v>0.01460371354187373</v>
       </c>
       <c r="O9" s="5">
         <v>7</v>
       </c>
       <c r="P9" s="4">
-        <v>0.3228738521512631</v>
+        <v>0.31686080190957</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.2875574745751006</v>
+        <v>0.2841214458655616</v>
       </c>
       <c r="R9" s="5">
         <v>7</v>
@@ -12830,16 +12830,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>0.2380746525535263</v>
+        <v>0.3052224480597943</v>
       </c>
       <c r="O10" s="5">
         <v>6</v>
       </c>
       <c r="P10" s="4">
-        <v>0.4612445254512446</v>
+        <v>0.4605387847350357</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.2404528538859773</v>
+        <v>0.2395118662643654</v>
       </c>
       <c r="R10" s="5">
         <v>6</v>
@@ -13126,7 +13126,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3912580299176625</v>
+        <v>-0.3576918691469473</v>
       </c>
       <c r="O3" s="5">
         <v>10</v>
@@ -13185,16 +13185,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2938838154092082</v>
+        <v>-0.3987893173725752</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
       </c>
       <c r="P4" s="4">
-        <v>0.5646064581841347</v>
+        <v>0.558767031179741</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.5646064581841347</v>
+        <v>0.558767031179741</v>
       </c>
       <c r="R4" s="5">
         <v>10</v>
@@ -13244,16 +13244,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.5702994096063776</v>
+        <v>-0.4800692446005996</v>
       </c>
       <c r="O5" s="5">
         <v>10</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4229247707844479</v>
+        <v>0.4073783214582363</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4229247707844479</v>
+        <v>0.4073783214582363</v>
       </c>
       <c r="R5" s="5">
         <v>10</v>
@@ -13303,13 +13303,13 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>0.6101997935611507</v>
+        <v>0.480722053162026</v>
       </c>
       <c r="O6" s="5">
         <v>8</v>
       </c>
       <c r="P6" s="4">
-        <v>0.60909388268974</v>
+        <v>0.583198334609915</v>
       </c>
       <c r="Q6" s="4">
         <v>0.5284211908465295</v>
@@ -13362,16 +13362,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.380702463536831</v>
+        <v>-0.2959375841164729</v>
       </c>
       <c r="O7" s="5">
         <v>7</v>
       </c>
       <c r="P7" s="4">
-        <v>0.4241135604653599</v>
+        <v>0.4261137509478431</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.3411971680046064</v>
+        <v>0.3093932695410331</v>
       </c>
       <c r="R7" s="5">
         <v>7</v>
@@ -13421,16 +13421,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.5128599572282317</v>
+        <v>-0.5894259295382653</v>
       </c>
       <c r="O8" s="5">
         <v>7</v>
       </c>
       <c r="P8" s="4">
-        <v>0.2025639981928555</v>
+        <v>0.1915409022258245</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.2191426601835256</v>
+        <v>0.2082046641392351</v>
       </c>
       <c r="R8" s="5">
         <v>7</v>
@@ -13480,16 +13480,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>0.2399305937738973</v>
+        <v>0.3649932199477917</v>
       </c>
       <c r="O9" s="5">
         <v>5</v>
       </c>
       <c r="P9" s="4">
-        <v>0.3705948699491273</v>
+        <v>0.3329909056519682</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.1995761071774177</v>
+        <v>0.164422289536742</v>
       </c>
       <c r="R9" s="5">
         <v>5</v>
@@ -13539,13 +13539,13 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.4230679772833052</v>
+        <v>-0.2780932107925764</v>
       </c>
       <c r="O10" s="5">
         <v>6</v>
       </c>
       <c r="P10" s="4">
-        <v>0.848873361771742</v>
+        <v>0.8851170533944241</v>
       </c>
       <c r="Q10" s="4">
         <v>0.3996060495943918</v>
@@ -13835,16 +13835,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2506831455029896</v>
+        <v>-0.215267895906436</v>
       </c>
       <c r="O3" s="5">
         <v>10</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1260699031598051</v>
+        <v>0.116984259164019</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1260699031598051</v>
+        <v>0.116984259164019</v>
       </c>
       <c r="R3" s="5">
         <v>10</v>
@@ -13894,16 +13894,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.106412120630921</v>
+        <v>-0.1783777325581468</v>
       </c>
       <c r="O4" s="5">
         <v>8</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3032846049965883</v>
+        <v>0.2804826621773827</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2657632090390507</v>
+        <v>0.2552521834968502</v>
       </c>
       <c r="R4" s="5">
         <v>8</v>
@@ -13953,16 +13953,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.3196820027870773</v>
+        <v>-0.3311911177370348</v>
       </c>
       <c r="O5" s="5">
         <v>9</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1742098100645106</v>
+        <v>0.171907987074519</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1302354365722334</v>
+        <v>0.1289566460222381</v>
       </c>
       <c r="R5" s="5">
         <v>9</v>
@@ -14012,22 +14012,22 @@
         <v>2</v>
       </c>
       <c r="N6" s="4">
-        <v>1.205907091214613</v>
+        <v>0.3304740618332289</v>
       </c>
       <c r="O6" s="5">
         <v>6</v>
       </c>
       <c r="P6" s="4">
-        <v>1.426769334496203</v>
+        <v>1.343593985036569</v>
       </c>
       <c r="Q6" s="4">
-        <v>1.166609338654962</v>
+        <v>0.2466602321474056</v>
       </c>
       <c r="R6" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S6" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="25" customHeight="1">
@@ -14071,20 +14071,22 @@
         <v>2</v>
       </c>
       <c r="N7" s="4">
-        <v>-4.124356912881012</v>
+        <v>0.03701600847489317</v>
       </c>
       <c r="O7" s="5">
         <v>8</v>
       </c>
       <c r="P7" s="4">
-        <v>5.131110219385664</v>
-      </c>
-      <c r="Q7" s="4"/>
+        <v>4.281848783072201</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.3041401376443294</v>
+      </c>
       <c r="R7" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S7" s="5">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="25" customHeight="1">
@@ -14128,16 +14130,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.2012650790857151</v>
+        <v>-0.1806189180861111</v>
       </c>
       <c r="O8" s="5">
         <v>8</v>
       </c>
       <c r="P8" s="4">
-        <v>0.1104769203714871</v>
+        <v>0.1102546601509352</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1030614665032772</v>
+        <v>0.1002306536302058</v>
       </c>
       <c r="R8" s="5">
         <v>8</v>
@@ -14187,16 +14189,16 @@
         <v>1</v>
       </c>
       <c r="N9" s="4">
-        <v>0.5787729686247379</v>
+        <v>0.06410407742441748</v>
       </c>
       <c r="O9" s="5">
         <v>6</v>
       </c>
       <c r="P9" s="4">
-        <v>1.163392039159589</v>
+        <v>1.195677985812836</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.5689137124179979</v>
+        <v>0.3117698923429998</v>
       </c>
       <c r="R9" s="5">
         <v>5</v>
@@ -14246,16 +14248,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>0.1892338205769192</v>
+        <v>0.1200268382526701</v>
       </c>
       <c r="O10" s="5">
         <v>5</v>
       </c>
       <c r="P10" s="4">
-        <v>0.296555965814332</v>
+        <v>0.2792542202332697</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.1876390223065391</v>
+        <v>0.1737976258416893</v>
       </c>
       <c r="R10" s="5">
         <v>5</v>
